--- a/data/tags/אלבומים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חנן בן ארי לא המשוגע היחידי</v>
+        <v>מאור כהן - אתה תגיד</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%97%d7%a0%d7%9f-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%9c%d7%90-%d7%94%d7%9e%d7%a9%d7%95%d7%92%d7%a2-%d7%94%d7%99%d7%97%d7%99%d7%93%d7%99/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24442&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>חנן בן ארי לא מנסה להמציא את עצמו מחדש – אלא מעז להסיר שכבות. זהו אלבום שמעדיף אמת על פני פוזה, פגיעות על פני הצהרה, ושאלות פתוחות על פני תשובות מהודקות. בין תפילה להמנון, בין בלדת נשמה לפולק־רוק אמריקאי ובין</v>
+        <v>18:55</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חנן בן ארי לא המשוגע היחידי</v>
+        <v>מאור כהן - אתה תגיד</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מאור כהן - אתה תגיד</v>
+        <v>לואיס טומלינסון How Did I Get Here</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24442&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%9c%d7%95%d7%90%d7%99%d7%a1-%d7%98%d7%95%d7%9e%d7%9c%d7%99%d7%a0%d7%a1%d7%95%d7%9f-how-did-i-get-here/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18:55</v>
+        <v>מוזיקת פופ היא עניין דו־צדדי: מצד אחד, היא לא הייתה נקראת פופ אם לא הייתה מכוונת לקהל רחב ככל האפשר, ומצד שני – בשל המהות שלה והאופן שבו היא נוצרת – היא זוכה לא פעם ליחס ספקני מצד מבקרי מוזיקה.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מאור כהן - אתה תגיד</v>
+        <v>לואיס טומלינסון How Did I Get Here</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>לואיס טומלינסון How Did I Get Here</v>
+        <v>ליידי גאגא MAYHEM אלבום הפופ הווקאלי הטוב ביותר בגראמי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9c%d7%95%d7%90%d7%99%d7%a1-%d7%98%d7%95%d7%9e%d7%9c%d7%99%d7%a0%d7%a1%d7%95%d7%9f-how-did-i-get-here/</v>
+        <v>https://yosmusic.com/%d7%9c%d7%99%d7%99%d7%93%d7%99-%d7%92%d7%90%d7%92%d7%90-mayhem/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מוזיקת פופ היא עניין דו־צדדי: מצד אחד, היא לא הייתה נקראת פופ אם לא הייתה מכוונת לקהל רחב ככל האפשר, ומצד שני – בשל המהות שלה והאופן שבו היא נוצרת – היא זוכה לא פעם ליחס ספקני מצד מבקרי מוזיקה.</v>
+        <v>כשליידי גאגא הכריזה לראשונה על 'Mayhem' בינואר, היא אמרה שזה "התחיל כשהתמודדתי עם הפחד שלי לחזור למוזיקת ​​הפופ שהמעריצים הראשונים שלי אהבו". היא לא ממש ניסתה לשחזר את הצליל של 2008 אבל גאגא התחברה לאזוור הרגשי הזה מחדש. "פנטום רחבת</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>לואיס טומלינסון How Did I Get Here</v>
+        <v>ליידי גאגא MAYHEM אלבום הפופ הווקאלי הטוב ביותר בגראמי</v>
       </c>
     </row>
   </sheetData>
